--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484023_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484023_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. BARBECHO GARCIA</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6147</v>
+        <v>10.1575</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8245</v>
+        <v>7.4786</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7903</v>
+        <v>2.6789</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2214</v>
+        <v>4.448</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7055</v>
+        <v>0.4941</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5159</v>
+        <v>3.9539</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0382</v>
+        <v>4.0008</v>
       </c>
       <c r="K2" t="n">
-        <v>4.235</v>
+        <v>1.6989</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8032</v>
+        <v>2.302</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1832</v>
+        <v>0.4472</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5295</v>
+        <v>-1.2048</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7127</v>
+        <v>1.652</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.579</v>
+        <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4565</v>
+        <v>1.0982</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4285</v>
+        <v>-0.1416</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0281</v>
+        <v>1.2398</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3417</v>
+        <v>3.6194</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3417</v>
+        <v>3.6194</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>P. BARBECHO GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.939500000000001</v>
+        <v>9.626200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0081</v>
+        <v>6.1726</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9314</v>
+        <v>3.4536</v>
       </c>
       <c r="G3" t="n">
-        <v>4.448</v>
+        <v>5.2214</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4941</v>
+        <v>3.7055</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9539</v>
+        <v>1.5159</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0008</v>
+        <v>5.0382</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6989</v>
+        <v>4.235</v>
       </c>
       <c r="L3" t="n">
-        <v>2.302</v>
+        <v>0.8032</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4472</v>
+        <v>0.1832</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2048</v>
+        <v>-0.5295</v>
       </c>
       <c r="O3" t="n">
-        <v>1.652</v>
+        <v>0.7127</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9919</v>
+        <v>2.579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8802</v>
+        <v>1.468</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6121</v>
+        <v>0.7766</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4923</v>
+        <v>0.6914</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6194</v>
+        <v>2.3417</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6194</v>
+        <v>2.3417</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7378</v>
+        <v>4.0976</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5062</v>
+        <v>1.894</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2317</v>
+        <v>2.2036</v>
       </c>
       <c r="G4" t="n">
         <v>4.2363</v>
@@ -766,13 +766,13 @@
         <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>1.608</v>
+        <v>0.9678</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7993</v>
+        <v>0.1871</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8087</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.4724</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4835</v>
+        <v>3.5995</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5292</v>
+        <v>1.1839</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9543</v>
+        <v>2.4156</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2638</v>
+        <v>2.9202</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6248</v>
+        <v>-0.267</v>
       </c>
       <c r="I5" t="n">
-        <v>1.639</v>
+        <v>3.1872</v>
       </c>
       <c r="J5" t="n">
-        <v>1.892</v>
+        <v>3.0042</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0887</v>
+        <v>0.3937</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8032</v>
+        <v>2.6105</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3718</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4639</v>
+        <v>-0.6607</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8357</v>
+        <v>0.5767</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4262</v>
+        <v>0.2664</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3627</v>
+        <v>-0.051</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7889</v>
+        <v>0.3173</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4659</v>
+        <v>3.5816</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6114000000000001</v>
+        <v>1.7956</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8545</v>
+        <v>1.7859</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9202</v>
+        <v>2.2638</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.267</v>
+        <v>0.6248</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1872</v>
+        <v>1.639</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0042</v>
+        <v>1.892</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3937</v>
+        <v>1.0887</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6105</v>
+        <v>0.8032</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.3718</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6607</v>
+        <v>-0.4639</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5767</v>
+        <v>0.8357</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1822</v>
+        <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8672</v>
+        <v>0.5243</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.0963</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2438</v>
+        <v>0.6206</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4203</v>
+        <v>2.451</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0364</v>
+        <v>0.8457</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4567</v>
+        <v>1.6053</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2735</v>
+        <v>0.5022</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0977</v>
+        <v>-0.5446</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8241000000000001</v>
+        <v>1.0468</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0711</v>
+        <v>0.7043</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1698</v>
+        <v>0.2472</v>
       </c>
       <c r="L7" t="n">
-        <v>0.241</v>
+        <v>0.4571</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3447</v>
+        <v>-0.2021</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9278</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5897</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1185</v>
+        <v>0.7071</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2414</v>
+        <v>-0.1246</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8771</v>
+        <v>0.8317</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.615</v>
+        <v>-0.9405</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.349</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5349</v>
+        <v>1.7157</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0565</v>
+        <v>0.0682</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5914</v>
+        <v>1.6475</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0207</v>
@@ -1078,13 +1078,13 @@
         <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1507</v>
+        <v>0.3315</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0679</v>
+        <v>0.0567</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2187</v>
+        <v>0.2748</v>
       </c>
       <c r="V8" t="n">
         <v>1.2065</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1935</v>
+        <v>0.8973</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2335</v>
+        <v>-0.83</v>
       </c>
       <c r="F9" t="n">
-        <v>0.96</v>
+        <v>1.7273</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5022</v>
+        <v>-0.2735</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5446</v>
+        <v>-1.0977</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0468</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7043</v>
+        <v>0.0711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2472</v>
+        <v>-0.1698</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4571</v>
+        <v>0.241</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2021</v>
+        <v>-0.3447</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.9278</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5897</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5504</v>
+        <v>1.5955</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7368</v>
+        <v>0.4479</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1864</v>
+        <v>1.1476</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9405</v>
+        <v>-1.615</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>-1.349</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. RIBAS BLANCO</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7343</v>
+        <v>-0.4721</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8832</v>
+        <v>-0.8818</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6175</v>
+        <v>0.4096</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3505</v>
+        <v>1.1888</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7661</v>
+        <v>1.497</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5843</v>
+        <v>-0.3083</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0079</v>
+        <v>0.7563</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9678</v>
+        <v>1.3561</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>-0.5999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3425</v>
+        <v>0.4325</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2016</v>
+        <v>0.1409</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5442</v>
+        <v>0.2916</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3968</v>
+        <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06859999999999999</v>
+        <v>0.3472</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1247</v>
+        <v>0.3458</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0561</v>
+        <v>0.0014</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4129</v>
+        <v>-1.8097</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4129</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>R. RIBAS BLANCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7768</v>
+        <v>-0.4857</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0462</v>
+        <v>1.0476</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2694</v>
+        <v>-1.5333</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1888</v>
+        <v>1.3505</v>
       </c>
       <c r="H11" t="n">
-        <v>1.497</v>
+        <v>0.7661</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3083</v>
+        <v>0.5843</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7563</v>
+        <v>1.0079</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3561</v>
+        <v>0.9678</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5999</v>
+        <v>0.0402</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4325</v>
+        <v>0.3425</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1409</v>
+        <v>-0.2016</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2916</v>
+        <v>0.5442</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0425</v>
+        <v>0.18</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1814</v>
+        <v>0.0397</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1389</v>
+        <v>0.1403</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8097</v>
+        <v>-2.4129</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8097</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8754</v>
+        <v>-0.5413</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8269</v>
+        <v>-0.5208</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0485</v>
+        <v>-0.0204</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9054</v>
@@ -1390,13 +1390,13 @@
         <v>0.1984</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1683</v>
+        <v>0.1658</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.187</v>
+        <v>0.1191</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>34.00360000000001</v>
+        <v>34.62730000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>17.6301</v>
+        <v>18.2536</v>
       </c>
       <c r="F13" t="n">
-        <v>16.3737</v>
+        <v>16.3736</v>
       </c>
       <c r="G13" t="n">
         <v>20.9316</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3193</v>
+        <v>5.319300000000001</v>
       </c>
       <c r="I13" t="n">
         <v>15.612</v>
@@ -1450,7 +1450,7 @@
         <v>10.5581</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.569</v>
+        <v>-0.5690000000000002</v>
       </c>
       <c r="N13" t="n">
         <v>-5.6229</v>
@@ -1459,7 +1459,7 @@
         <v>5.0541</v>
       </c>
       <c r="P13" t="n">
-        <v>2.975799999999999</v>
+        <v>2.9758</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.8949</v>
@@ -1468,13 +1468,13 @@
         <v>15.8707</v>
       </c>
       <c r="S13" t="n">
-        <v>7.028100000000001</v>
+        <v>7.6518</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9359000000000002</v>
+        <v>1.5594</v>
       </c>
       <c r="U13" t="n">
-        <v>6.092300000000001</v>
+        <v>6.0924</v>
       </c>
       <c r="V13" t="n">
         <v>3.0684</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3306</v>
+        <v>1.2107</v>
       </c>
       <c r="E14" t="n">
-        <v>0.423</v>
+        <v>0.2189</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9076</v>
+        <v>0.9918</v>
       </c>
       <c r="G14" t="n">
         <v>0.2481</v>
@@ -1546,13 +1546,13 @@
         <v>0.5952</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0788</v>
+        <v>-0.0411</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1304</v>
+        <v>-0.0736</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0516</v>
+        <v>0.0325</v>
       </c>
       <c r="V14" t="n">
         <v>0.4085</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MEDORI MORALES</t>
+          <t>J. MESADO PLANELLS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4195</v>
+        <v>-0.6684</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6943</v>
+        <v>-0.1622</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.1137</v>
+        <v>-0.5062</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5835</v>
+        <v>-0.418</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3052</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7218</v>
+        <v>-1.2139</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4375</v>
+        <v>0.1608</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7755</v>
+        <v>0.0403</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6619</v>
+        <v>0.1205</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.854</v>
+        <v>-0.5788</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.4703</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3837</v>
+        <v>-1.3344</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1822</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3226</v>
+        <v>-0.3217</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2326</v>
+        <v>-0.323</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09</v>
+        <v>0.0014</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.532</v>
+        <v>0.0713</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.532</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MESADO PLANELLS</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6863</v>
+        <v>-0.8017</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2643</v>
+        <v>1.3074</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.422</v>
+        <v>-2.1091</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.418</v>
+        <v>1.5355</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.6197</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2139</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1608</v>
+        <v>2.975</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0403</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1205</v>
+        <v>2.3797</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5788</v>
+        <v>-1.4395</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.0244</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3344</v>
+        <v>-1.4639</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3395</v>
+        <v>-1.3291</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4251</v>
+        <v>-1.1562</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.173</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0713</v>
+        <v>-1.2065</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0713</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>J. MEDORI MORALES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0619</v>
+        <v>-1.3981</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1034</v>
+        <v>1.776</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1652</v>
+        <v>-3.1741</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5355</v>
+        <v>0.5835</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6197</v>
+        <v>1.3052</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9157999999999999</v>
+        <v>-0.7218</v>
       </c>
       <c r="J17" t="n">
-        <v>2.975</v>
+        <v>5.4375</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5953000000000001</v>
+        <v>3.7755</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3797</v>
+        <v>1.6619</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4395</v>
+        <v>-4.854</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0244</v>
+        <v>-2.4703</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4639</v>
+        <v>-2.3837</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R17" t="n">
         <v>2.1822</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5893</v>
+        <v>-0.656</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3602</v>
+        <v>-0.6857</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2291</v>
+        <v>0.0297</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6789</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3184</v>
+        <v>-1.7156</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.8334</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0498</v>
+        <v>-2.549</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1624</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5366</v>
+        <v>-0.9338</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.68</v>
+        <v>-0.578</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8565</v>
+        <v>-0.3558</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2065</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6305</v>
+        <v>-3.3882</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9719</v>
+        <v>-1.8699</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6586</v>
+        <v>-1.5183</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6957</v>
@@ -1936,13 +1936,13 @@
         <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9267</v>
+        <v>-0.6844</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7481</v>
+        <v>-0.6461</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1786</v>
+        <v>-0.0383</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2065</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.9275</v>
+        <v>-6.6613</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8208</v>
+        <v>-4.7188</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1067</v>
+        <v>-1.9426</v>
       </c>
       <c r="G20" t="n">
         <v>-6.2157</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5538</v>
+        <v>-0.2876</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3683</v>
+        <v>-0.2663</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1854</v>
+        <v>-0.0213</v>
       </c>
       <c r="V20" t="n">
         <v>3.0162</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>D. MARTIN VELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.511100000000001</v>
+        <v>-9.926399999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.2445</v>
+        <v>-5.6159</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2666</v>
+        <v>-4.3105</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.4163</v>
+        <v>-5.3903</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3969</v>
+        <v>-0.6303</v>
       </c>
       <c r="I21" t="n">
-        <v>-7.0195</v>
+        <v>-4.76</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7688</v>
+        <v>-2.2067</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8669</v>
+        <v>0.4287</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.6358</v>
+        <v>-2.6354</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.6475</v>
+        <v>-3.1836</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2638</v>
+        <v>-1.059</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.3837</v>
+        <v>-2.1246</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5871</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3769</v>
+        <v>-1.254</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3772</v>
+        <v>-1.0882</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0002</v>
+        <v>-0.1658</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8692</v>
+        <v>-3.2821</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8692</v>
+        <v>-0.3373</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.9449</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MARTIN VELA</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.7792</v>
+        <v>-9.974500000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.024</v>
+        <v>-8.1425</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.7552</v>
+        <v>-1.832</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.3903</v>
+        <v>-8.4163</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6303</v>
+        <v>-1.3969</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.76</v>
+        <v>-7.0195</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2067</v>
+        <v>-3.7688</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4287</v>
+        <v>0.8669</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6354</v>
+        <v>-4.6358</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1836</v>
+        <v>-4.6475</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.059</v>
+        <v>-2.2638</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1246</v>
+        <v>-2.3837</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1068</v>
+        <v>-0.8403</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4963</v>
+        <v>-1.2752</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6105</v>
+        <v>0.4349</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.2821</v>
+        <v>0.8692</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3373</v>
+        <v>0.8692</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.9449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-34.0038</v>
+        <v>-33.3235</v>
       </c>
       <c r="E23" t="n">
-        <v>-16.3734</v>
+        <v>-16.3736</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.6302</v>
+        <v>-16.95</v>
       </c>
       <c r="G23" t="n">
         <v>-20.9313</v>
@@ -2227,7 +2227,7 @@
         <v>5.622800000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.0541</v>
+        <v>-5.054099999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-21.5003</v>
@@ -2239,7 +2239,7 @@
         <v>-10.5581</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.975600000000001</v>
+        <v>-2.9756</v>
       </c>
       <c r="Q23" t="n">
         <v>-15.8707</v>
@@ -2248,19 +2248,19 @@
         <v>12.8949</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.028199999999999</v>
+        <v>-6.348</v>
       </c>
       <c r="T23" t="n">
-        <v>-6.0922</v>
+        <v>-6.0923</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9360000000000002</v>
+        <v>-0.2556999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0684</v>
       </c>
       <c r="W23" t="n">
-        <v>5.020499999999999</v>
+        <v>5.0205</v>
       </c>
       <c r="X23" t="n">
         <v>-8.089</v>
